--- a/outputs/06_测试数据/发动机主线业务流程-多工厂一级工艺版/导入包/工厂资源_模板.xlsx
+++ b/outputs/06_测试数据/发动机主线业务流程-多工厂一级工艺版/导入包/工厂资源_模板.xlsx
@@ -1266,122 +1266,106 @@
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Eq101</t>
+          <t>EQ-MC-01</t>
         </is>
       </c>
       <c r="B2" s="44" t="inlineStr">
         <is>
-          <t>Wc101</t>
+          <t>WC-MC-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="44" t="inlineStr">
         <is>
-          <t>Eq102</t>
+          <t>EQ-QC-MC-01</t>
         </is>
       </c>
       <c r="B3" s="44" t="inlineStr">
         <is>
-          <t>Wc102</t>
+          <t>WC-QC-MC-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="44" t="inlineStr">
         <is>
-          <t>Eq201</t>
+          <t>EQ-SH-01</t>
         </is>
       </c>
       <c r="B4" s="44" t="inlineStr">
         <is>
-          <t>Wc201</t>
+          <t>WC-SH-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>Eq202</t>
+          <t>EQ-QC-SH-01</t>
         </is>
       </c>
       <c r="B5" s="44" t="inlineStr">
         <is>
-          <t>Wc202</t>
+          <t>WC-QC-SH-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="44" t="inlineStr">
         <is>
-          <t>Eq203</t>
+          <t>EQ-BL-01</t>
         </is>
       </c>
       <c r="B6" s="44" t="inlineStr">
         <is>
-          <t>Wc203</t>
+          <t>WC-BL-01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>Eq301</t>
+          <t>EQ-QC-BL-01</t>
         </is>
       </c>
       <c r="B7" s="44" t="inlineStr">
         <is>
-          <t>Wc301</t>
+          <t>WC-QC-BL-01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="44" t="inlineStr">
         <is>
-          <t>Eq302</t>
+          <t>EQ-ASM-01</t>
         </is>
       </c>
       <c r="B8" s="44" t="inlineStr">
         <is>
-          <t>Wc302</t>
+          <t>WC-ASM-01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>Eq303</t>
+          <t>EQ-QC-ASM-01</t>
         </is>
       </c>
       <c r="B9" s="44" t="inlineStr">
         <is>
-          <t>Wc303</t>
+          <t>WC-QC-ASM-01</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>Eq401</t>
-        </is>
-      </c>
-      <c r="B10" s="44" t="inlineStr">
-        <is>
-          <t>Wc401</t>
-        </is>
-      </c>
+      <c r="A10" s="44" t="inlineStr"/>
+      <c r="B10" s="44" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>Eq402</t>
-        </is>
-      </c>
-      <c r="B11" s="44" t="inlineStr">
-        <is>
-          <t>Wc402</t>
-        </is>
-      </c>
+      <c r="A11" s="44" t="inlineStr"/>
+      <c r="B11" s="44" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="44" t="inlineStr"/>
@@ -1818,7 +1802,7 @@
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Biz010</t>
+          <t>ORG-MC-001</t>
         </is>
       </c>
       <c r="B2" s="44" t="inlineStr"/>
@@ -1840,12 +1824,12 @@
       </c>
       <c r="G2" s="44" t="inlineStr">
         <is>
-          <t>Wh010</t>
+          <t>WH-MC-01</t>
         </is>
       </c>
       <c r="H2" s="44" t="inlineStr">
         <is>
-          <t>存放机匣毛坯与机加完件</t>
+          <t>存放机匣毛坯与机加完件。</t>
         </is>
       </c>
       <c r="I2" s="44" t="inlineStr">
@@ -1857,7 +1841,7 @@
     <row r="3">
       <c r="A3" s="44" t="inlineStr">
         <is>
-          <t>Biz020</t>
+          <t>ORG-SH-001</t>
         </is>
       </c>
       <c r="B3" s="44" t="inlineStr"/>
@@ -1879,12 +1863,12 @@
       </c>
       <c r="G3" s="44" t="inlineStr">
         <is>
-          <t>Wh020</t>
+          <t>WH-SH-01</t>
         </is>
       </c>
       <c r="H3" s="44" t="inlineStr">
         <is>
-          <t>存放盘轴锻件与盘轴模块</t>
+          <t>存放盘轴毛坯与盘轴组件。</t>
         </is>
       </c>
       <c r="I3" s="44" t="inlineStr">
@@ -1896,7 +1880,7 @@
     <row r="4">
       <c r="A4" s="44" t="inlineStr">
         <is>
-          <t>Biz030</t>
+          <t>ORG-BL-001</t>
         </is>
       </c>
       <c r="B4" s="44" t="inlineStr"/>
@@ -1918,12 +1902,12 @@
       </c>
       <c r="G4" s="44" t="inlineStr">
         <is>
-          <t>Wh030</t>
+          <t>WH-BL-01</t>
         </is>
       </c>
       <c r="H4" s="44" t="inlineStr">
         <is>
-          <t>存放叶片毛坯、涂层件与叶片组件</t>
+          <t>存放叶片毛坯与叶片组件套。</t>
         </is>
       </c>
       <c r="I4" s="44" t="inlineStr">
@@ -1935,14 +1919,14 @@
     <row r="5">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>Biz040</t>
+          <t>ORG-AS-001</t>
         </is>
       </c>
       <c r="B5" s="44" t="inlineStr"/>
       <c r="C5" s="44" t="inlineStr"/>
       <c r="D5" s="44" t="inlineStr">
         <is>
-          <t>装配成套库</t>
+          <t>装配原材料库</t>
         </is>
       </c>
       <c r="E5" s="44" t="inlineStr">
@@ -1957,12 +1941,12 @@
       </c>
       <c r="G5" s="44" t="inlineStr">
         <is>
-          <t>Wh040</t>
+          <t>WH-ASM-RAW</t>
         </is>
       </c>
       <c r="H5" s="44" t="inlineStr">
         <is>
-          <t>存放总装齐套件、成套包装件与待发运总成</t>
+          <t>装配厂齐套与装入物料。</t>
         </is>
       </c>
       <c r="I5" s="44" t="inlineStr">
@@ -1972,26 +1956,82 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="inlineStr"/>
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>ORG-AS-001</t>
+        </is>
+      </c>
       <c r="B6" s="44" t="inlineStr"/>
       <c r="C6" s="44" t="inlineStr"/>
-      <c r="D6" s="44" t="inlineStr"/>
-      <c r="E6" s="44" t="inlineStr"/>
-      <c r="F6" s="44" t="inlineStr"/>
-      <c r="G6" s="44" t="inlineStr"/>
-      <c r="H6" s="44" t="inlineStr"/>
-      <c r="I6" s="44" t="inlineStr"/>
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>发动机成品库</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="inlineStr">
+        <is>
+          <t>普通库房</t>
+        </is>
+      </c>
+      <c r="F6" s="44" t="inlineStr">
+        <is>
+          <t>ERP一级库</t>
+        </is>
+      </c>
+      <c r="G6" s="44" t="inlineStr">
+        <is>
+          <t>WH-FG-01</t>
+        </is>
+      </c>
+      <c r="H6" s="44" t="inlineStr">
+        <is>
+          <t>装配厂合格完工入库。</t>
+        </is>
+      </c>
+      <c r="I6" s="44" t="inlineStr">
+        <is>
+          <t>公开</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="44" t="inlineStr"/>
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t>ORG-AS-001</t>
+        </is>
+      </c>
       <c r="B7" s="44" t="inlineStr"/>
       <c r="C7" s="44" t="inlineStr"/>
-      <c r="D7" s="44" t="inlineStr"/>
-      <c r="E7" s="44" t="inlineStr"/>
-      <c r="F7" s="44" t="inlineStr"/>
-      <c r="G7" s="44" t="inlineStr"/>
-      <c r="H7" s="44" t="inlineStr"/>
-      <c r="I7" s="44" t="inlineStr"/>
+      <c r="D7" s="44" t="inlineStr">
+        <is>
+          <t>废品库</t>
+        </is>
+      </c>
+      <c r="E7" s="44" t="inlineStr">
+        <is>
+          <t>普通库房</t>
+        </is>
+      </c>
+      <c r="F7" s="44" t="inlineStr">
+        <is>
+          <t>ERP一级库</t>
+        </is>
+      </c>
+      <c r="G7" s="44" t="inlineStr">
+        <is>
+          <t>WH-SCR-01</t>
+        </is>
+      </c>
+      <c r="H7" s="44" t="inlineStr">
+        <is>
+          <t>装配厂报废隔离库存放。</t>
+        </is>
+      </c>
+      <c r="I7" s="44" t="inlineStr">
+        <is>
+          <t>公开</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="44" t="inlineStr"/>
@@ -3101,26 +3141,30 @@
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Biz010</t>
+          <t>ORG-MC-001</t>
         </is>
       </c>
       <c r="B2" s="44" t="inlineStr"/>
       <c r="C2" s="44" t="inlineStr">
         <is>
-          <t>Wh010</t>
+          <t>WH-MC-01</t>
         </is>
       </c>
       <c r="D2" s="44" t="inlineStr">
         <is>
-          <t>机匣毛坯区</t>
+          <t>MC-01-01</t>
         </is>
       </c>
       <c r="E2" s="44" t="inlineStr">
         <is>
-          <t>Loc011</t>
-        </is>
-      </c>
-      <c r="F2" s="44" t="inlineStr"/>
+          <t>LOC-MC-01</t>
+        </is>
+      </c>
+      <c r="F2" s="44" t="inlineStr">
+        <is>
+          <t>机匣毛坯区。</t>
+        </is>
+      </c>
       <c r="G2" s="44" t="inlineStr">
         <is>
           <t>公开</t>
@@ -3130,26 +3174,30 @@
     <row r="3">
       <c r="A3" s="44" t="inlineStr">
         <is>
-          <t>Biz010</t>
+          <t>ORG-MC-001</t>
         </is>
       </c>
       <c r="B3" s="44" t="inlineStr"/>
       <c r="C3" s="44" t="inlineStr">
         <is>
-          <t>Wh010</t>
+          <t>WH-MC-01</t>
         </is>
       </c>
       <c r="D3" s="44" t="inlineStr">
         <is>
-          <t>机加完件区</t>
+          <t>MC-01-02</t>
         </is>
       </c>
       <c r="E3" s="44" t="inlineStr">
         <is>
-          <t>Loc012</t>
-        </is>
-      </c>
-      <c r="F3" s="44" t="inlineStr"/>
+          <t>LOC-MC-02</t>
+        </is>
+      </c>
+      <c r="F3" s="44" t="inlineStr">
+        <is>
+          <t>机匣完件区。</t>
+        </is>
+      </c>
       <c r="G3" s="44" t="inlineStr">
         <is>
           <t>公开</t>
@@ -3159,26 +3207,30 @@
     <row r="4">
       <c r="A4" s="44" t="inlineStr">
         <is>
-          <t>Biz010</t>
+          <t>ORG-SH-001</t>
         </is>
       </c>
       <c r="B4" s="44" t="inlineStr"/>
       <c r="C4" s="44" t="inlineStr">
         <is>
-          <t>Wh010</t>
+          <t>WH-SH-01</t>
         </is>
       </c>
       <c r="D4" s="44" t="inlineStr">
         <is>
-          <t>待发装配区</t>
+          <t>SH-01-01</t>
         </is>
       </c>
       <c r="E4" s="44" t="inlineStr">
         <is>
-          <t>Loc013</t>
-        </is>
-      </c>
-      <c r="F4" s="44" t="inlineStr"/>
+          <t>LOC-SH-01</t>
+        </is>
+      </c>
+      <c r="F4" s="44" t="inlineStr">
+        <is>
+          <t>盘轴毛坯区。</t>
+        </is>
+      </c>
       <c r="G4" s="44" t="inlineStr">
         <is>
           <t>公开</t>
@@ -3188,26 +3240,30 @@
     <row r="5">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>Biz020</t>
+          <t>ORG-SH-001</t>
         </is>
       </c>
       <c r="B5" s="44" t="inlineStr"/>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>Wh020</t>
+          <t>WH-SH-01</t>
         </is>
       </c>
       <c r="D5" s="44" t="inlineStr">
         <is>
-          <t>盘轴锻件区</t>
+          <t>SH-01-02</t>
         </is>
       </c>
       <c r="E5" s="44" t="inlineStr">
         <is>
-          <t>Loc021</t>
-        </is>
-      </c>
-      <c r="F5" s="44" t="inlineStr"/>
+          <t>LOC-SH-02</t>
+        </is>
+      </c>
+      <c r="F5" s="44" t="inlineStr">
+        <is>
+          <t>盘轴完件区。</t>
+        </is>
+      </c>
       <c r="G5" s="44" t="inlineStr">
         <is>
           <t>公开</t>
@@ -3217,26 +3273,30 @@
     <row r="6">
       <c r="A6" s="44" t="inlineStr">
         <is>
-          <t>Biz020</t>
+          <t>ORG-BL-001</t>
         </is>
       </c>
       <c r="B6" s="44" t="inlineStr"/>
       <c r="C6" s="44" t="inlineStr">
         <is>
-          <t>Wh020</t>
+          <t>WH-BL-01</t>
         </is>
       </c>
       <c r="D6" s="44" t="inlineStr">
         <is>
-          <t>平衡待检区</t>
+          <t>BL-01-01</t>
         </is>
       </c>
       <c r="E6" s="44" t="inlineStr">
         <is>
-          <t>Loc022</t>
-        </is>
-      </c>
-      <c r="F6" s="44" t="inlineStr"/>
+          <t>LOC-BL-01</t>
+        </is>
+      </c>
+      <c r="F6" s="44" t="inlineStr">
+        <is>
+          <t>叶片毛坯区。</t>
+        </is>
+      </c>
       <c r="G6" s="44" t="inlineStr">
         <is>
           <t>公开</t>
@@ -3246,26 +3306,30 @@
     <row r="7">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>Biz020</t>
+          <t>ORG-BL-001</t>
         </is>
       </c>
       <c r="B7" s="44" t="inlineStr"/>
       <c r="C7" s="44" t="inlineStr">
         <is>
-          <t>Wh020</t>
+          <t>WH-BL-01</t>
         </is>
       </c>
       <c r="D7" s="44" t="inlineStr">
         <is>
-          <t>盘轴合格区</t>
+          <t>BL-01-02</t>
         </is>
       </c>
       <c r="E7" s="44" t="inlineStr">
         <is>
-          <t>Loc023</t>
-        </is>
-      </c>
-      <c r="F7" s="44" t="inlineStr"/>
+          <t>LOC-BL-02</t>
+        </is>
+      </c>
+      <c r="F7" s="44" t="inlineStr">
+        <is>
+          <t>叶片组件区。</t>
+        </is>
+      </c>
       <c r="G7" s="44" t="inlineStr">
         <is>
           <t>公开</t>
@@ -3275,26 +3339,30 @@
     <row r="8">
       <c r="A8" s="44" t="inlineStr">
         <is>
-          <t>Biz030</t>
+          <t>ORG-AS-001</t>
         </is>
       </c>
       <c r="B8" s="44" t="inlineStr"/>
       <c r="C8" s="44" t="inlineStr">
         <is>
-          <t>Wh030</t>
+          <t>WH-ASM-RAW</t>
         </is>
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>叶片毛坯区</t>
+          <t>A-01-01</t>
         </is>
       </c>
       <c r="E8" s="44" t="inlineStr">
         <is>
-          <t>Loc031</t>
-        </is>
-      </c>
-      <c r="F8" s="44" t="inlineStr"/>
+          <t>LOC-ASM-RAW-01</t>
+        </is>
+      </c>
+      <c r="F8" s="44" t="inlineStr">
+        <is>
+          <t>装配原材料库主库位。</t>
+        </is>
+      </c>
       <c r="G8" s="44" t="inlineStr">
         <is>
           <t>公开</t>
@@ -3304,26 +3372,30 @@
     <row r="9">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>Biz030</t>
+          <t>ORG-AS-001</t>
         </is>
       </c>
       <c r="B9" s="44" t="inlineStr"/>
       <c r="C9" s="44" t="inlineStr">
         <is>
-          <t>Wh030</t>
+          <t>WH-FG-01</t>
         </is>
       </c>
       <c r="D9" s="44" t="inlineStr">
         <is>
-          <t>涂层待检区</t>
+          <t>FG-01-01</t>
         </is>
       </c>
       <c r="E9" s="44" t="inlineStr">
         <is>
-          <t>Loc032</t>
-        </is>
-      </c>
-      <c r="F9" s="44" t="inlineStr"/>
+          <t>LOC-FG-01</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>发动机成品库位。</t>
+        </is>
+      </c>
       <c r="G9" s="44" t="inlineStr">
         <is>
           <t>公开</t>
@@ -3333,26 +3405,30 @@
     <row r="10">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>Biz030</t>
+          <t>ORG-AS-001</t>
         </is>
       </c>
       <c r="B10" s="44" t="inlineStr"/>
       <c r="C10" s="44" t="inlineStr">
         <is>
-          <t>Wh030</t>
+          <t>WH-SCR-01</t>
         </is>
       </c>
       <c r="D10" s="44" t="inlineStr">
         <is>
-          <t>叶片合格区</t>
+          <t>SCR-01-01</t>
         </is>
       </c>
       <c r="E10" s="44" t="inlineStr">
         <is>
-          <t>Loc033</t>
-        </is>
-      </c>
-      <c r="F10" s="44" t="inlineStr"/>
+          <t>LOC-SCR-01</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="inlineStr">
+        <is>
+          <t>报废库存放库位。</t>
+        </is>
+      </c>
       <c r="G10" s="44" t="inlineStr">
         <is>
           <t>公开</t>
@@ -3360,91 +3436,31 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>Biz040</t>
-        </is>
-      </c>
+      <c r="A11" s="44" t="inlineStr"/>
       <c r="B11" s="44" t="inlineStr"/>
-      <c r="C11" s="44" t="inlineStr">
-        <is>
-          <t>Wh040</t>
-        </is>
-      </c>
-      <c r="D11" s="44" t="inlineStr">
-        <is>
-          <t>总装齐套区</t>
-        </is>
-      </c>
-      <c r="E11" s="44" t="inlineStr">
-        <is>
-          <t>Loc041</t>
-        </is>
-      </c>
+      <c r="C11" s="44" t="inlineStr"/>
+      <c r="D11" s="44" t="inlineStr"/>
+      <c r="E11" s="44" t="inlineStr"/>
       <c r="F11" s="44" t="inlineStr"/>
-      <c r="G11" s="44" t="inlineStr">
-        <is>
-          <t>公开</t>
-        </is>
-      </c>
+      <c r="G11" s="44" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="44" t="inlineStr">
-        <is>
-          <t>Biz040</t>
-        </is>
-      </c>
+      <c r="A12" s="44" t="inlineStr"/>
       <c r="B12" s="44" t="inlineStr"/>
-      <c r="C12" s="44" t="inlineStr">
-        <is>
-          <t>Wh040</t>
-        </is>
-      </c>
-      <c r="D12" s="44" t="inlineStr">
-        <is>
-          <t>试车待放行区</t>
-        </is>
-      </c>
-      <c r="E12" s="44" t="inlineStr">
-        <is>
-          <t>Loc042</t>
-        </is>
-      </c>
+      <c r="C12" s="44" t="inlineStr"/>
+      <c r="D12" s="44" t="inlineStr"/>
+      <c r="E12" s="44" t="inlineStr"/>
       <c r="F12" s="44" t="inlineStr"/>
-      <c r="G12" s="44" t="inlineStr">
-        <is>
-          <t>公开</t>
-        </is>
-      </c>
+      <c r="G12" s="44" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="44" t="inlineStr">
-        <is>
-          <t>Biz040</t>
-        </is>
-      </c>
+      <c r="A13" s="44" t="inlineStr"/>
       <c r="B13" s="44" t="inlineStr"/>
-      <c r="C13" s="44" t="inlineStr">
-        <is>
-          <t>Wh040</t>
-        </is>
-      </c>
-      <c r="D13" s="44" t="inlineStr">
-        <is>
-          <t>发运成套区</t>
-        </is>
-      </c>
-      <c r="E13" s="44" t="inlineStr">
-        <is>
-          <t>Loc043</t>
-        </is>
-      </c>
+      <c r="C13" s="44" t="inlineStr"/>
+      <c r="D13" s="44" t="inlineStr"/>
+      <c r="E13" s="44" t="inlineStr"/>
       <c r="F13" s="44" t="inlineStr"/>
-      <c r="G13" s="44" t="inlineStr">
-        <is>
-          <t>公开</t>
-        </is>
-      </c>
+      <c r="G13" s="44" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="44" t="inlineStr"/>
@@ -4348,7 +4364,7 @@
       </c>
       <c r="C2" s="44" t="inlineStr">
         <is>
-          <t>机匣毛坯上线与找正</t>
+          <t>10-机加厂</t>
         </is>
       </c>
       <c r="D2" s="44" t="inlineStr"/>
@@ -4359,14 +4375,14 @@
       </c>
       <c r="F2" s="44" t="inlineStr">
         <is>
-          <t>Wc101</t>
+          <t>WC-PD-MC-01</t>
         </is>
       </c>
       <c r="G2" s="44" t="n">
         <v>10</v>
       </c>
       <c r="H2" s="44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" s="44" t="inlineStr">
         <is>
@@ -4383,7 +4399,7 @@
       </c>
       <c r="L2" s="44" t="inlineStr">
         <is>
-          <t>完成机匣毛坯上线、找正和工艺准备。</t>
+          <t>生产部协同机加厂完成机匣组件交付。</t>
         </is>
       </c>
       <c r="M2" s="44" t="inlineStr">
@@ -4401,7 +4417,7 @@
       </c>
       <c r="C3" s="44" t="inlineStr">
         <is>
-          <t>机匣五轴粗精加工</t>
+          <t>20-盘轴厂</t>
         </is>
       </c>
       <c r="D3" s="44" t="inlineStr"/>
@@ -4412,14 +4428,14 @@
       </c>
       <c r="F3" s="44" t="inlineStr">
         <is>
-          <t>Wc101</t>
+          <t>WC-PD-SH-01</t>
         </is>
       </c>
       <c r="G3" s="44" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H3" s="44" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I3" s="44" t="inlineStr">
         <is>
@@ -4436,7 +4452,7 @@
       </c>
       <c r="L3" s="44" t="inlineStr">
         <is>
-          <t>完成机匣关键孔面、安装面和外形粗精加工。</t>
+          <t>生产部协同盘轴厂完成盘轴组件交付。</t>
         </is>
       </c>
       <c r="M3" s="44" t="inlineStr">
@@ -4454,25 +4470,25 @@
       </c>
       <c r="C4" s="44" t="inlineStr">
         <is>
-          <t>机匣尺寸终检</t>
+          <t>30-叶片厂</t>
         </is>
       </c>
       <c r="D4" s="44" t="inlineStr"/>
       <c r="E4" s="44" t="inlineStr">
         <is>
-          <t>检验</t>
+          <t>加工</t>
         </is>
       </c>
       <c r="F4" s="44" t="inlineStr">
         <is>
-          <t>Wc102</t>
+          <t>WC-PD-BL-01</t>
         </is>
       </c>
       <c r="G4" s="44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H4" s="44" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I4" s="44" t="inlineStr">
         <is>
@@ -4489,7 +4505,7 @@
       </c>
       <c r="L4" s="44" t="inlineStr">
         <is>
-          <t>完成机匣尺寸、同轴度和表面质量终检。</t>
+          <t>生产部协同叶片厂完成叶片组件套交付。</t>
         </is>
       </c>
       <c r="M4" s="44" t="inlineStr">
@@ -4507,7 +4523,7 @@
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>盘轴复合加工</t>
+          <t>40-装配厂</t>
         </is>
       </c>
       <c r="D5" s="44" t="inlineStr"/>
@@ -4518,7 +4534,7 @@
       </c>
       <c r="F5" s="44" t="inlineStr">
         <is>
-          <t>Wc201</t>
+          <t>WC-PD-AS-01</t>
         </is>
       </c>
       <c r="G5" s="44" t="n">
@@ -4542,7 +4558,7 @@
       </c>
       <c r="L5" s="44" t="inlineStr">
         <is>
-          <t>完成盘轴类关键件车铣复合加工。</t>
+          <t>生产部协同装配厂完成总装试车与交付。</t>
         </is>
       </c>
       <c r="M5" s="44" t="inlineStr">
@@ -4560,7 +4576,7 @@
       </c>
       <c r="C6" s="44" t="inlineStr">
         <is>
-          <t>盘轴动平衡修正</t>
+          <t>机匣粗加工</t>
         </is>
       </c>
       <c r="D6" s="44" t="inlineStr"/>
@@ -4571,14 +4587,14 @@
       </c>
       <c r="F6" s="44" t="inlineStr">
         <is>
-          <t>Wc202</t>
+          <t>WC-MC-01</t>
         </is>
       </c>
       <c r="G6" s="44" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H6" s="44" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I6" s="44" t="inlineStr">
         <is>
@@ -4595,7 +4611,7 @@
       </c>
       <c r="L6" s="44" t="inlineStr">
         <is>
-          <t>完成盘轴动平衡检测与修正。</t>
+          <t>完成机匣毛坯装夹、粗加工与找正。</t>
         </is>
       </c>
       <c r="M6" s="44" t="inlineStr">
@@ -4613,25 +4629,25 @@
       </c>
       <c r="C7" s="44" t="inlineStr">
         <is>
-          <t>盘轴终检放行</t>
+          <t>机匣精加工</t>
         </is>
       </c>
       <c r="D7" s="44" t="inlineStr"/>
       <c r="E7" s="44" t="inlineStr">
         <is>
-          <t>检验</t>
+          <t>加工</t>
         </is>
       </c>
       <c r="F7" s="44" t="inlineStr">
         <is>
-          <t>Wc203</t>
+          <t>WC-MC-01</t>
         </is>
       </c>
       <c r="G7" s="44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7" s="44" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I7" s="44" t="inlineStr">
         <is>
@@ -4648,7 +4664,7 @@
       </c>
       <c r="L7" s="44" t="inlineStr">
         <is>
-          <t>完成盘轴无损、尺寸和外观终检。</t>
+          <t>完成机匣关键孔面与装配基准精加工。</t>
         </is>
       </c>
       <c r="M7" s="44" t="inlineStr">
@@ -4666,25 +4682,25 @@
       </c>
       <c r="C8" s="44" t="inlineStr">
         <is>
-          <t>叶片成型加工</t>
+          <t>机匣终检</t>
         </is>
       </c>
       <c r="D8" s="44" t="inlineStr"/>
       <c r="E8" s="44" t="inlineStr">
         <is>
-          <t>加工</t>
+          <t>检验</t>
         </is>
       </c>
       <c r="F8" s="44" t="inlineStr">
         <is>
-          <t>Wc301</t>
+          <t>WC-QC-MC-01</t>
         </is>
       </c>
       <c r="G8" s="44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H8" s="44" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I8" s="44" t="inlineStr">
         <is>
@@ -4701,7 +4717,7 @@
       </c>
       <c r="L8" s="44" t="inlineStr">
         <is>
-          <t>完成叶片型面成型和冷端修整。</t>
+          <t>完成机匣组件尺寸终检与放行。</t>
         </is>
       </c>
       <c r="M8" s="44" t="inlineStr">
@@ -4719,7 +4735,7 @@
       </c>
       <c r="C9" s="44" t="inlineStr">
         <is>
-          <t>叶片表面涂层处理</t>
+          <t>盘轴加工</t>
         </is>
       </c>
       <c r="D9" s="44" t="inlineStr"/>
@@ -4730,14 +4746,14 @@
       </c>
       <c r="F9" s="44" t="inlineStr">
         <is>
-          <t>Wc302</t>
+          <t>WC-SH-01</t>
         </is>
       </c>
       <c r="G9" s="44" t="n">
         <v>12</v>
       </c>
       <c r="H9" s="44" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I9" s="44" t="inlineStr">
         <is>
@@ -4754,7 +4770,7 @@
       </c>
       <c r="L9" s="44" t="inlineStr">
         <is>
-          <t>完成叶片保护涂层喷涂和固化。</t>
+          <t>完成盘轴毛坯复合加工。</t>
         </is>
       </c>
       <c r="M9" s="44" t="inlineStr">
@@ -4772,25 +4788,25 @@
       </c>
       <c r="C10" s="44" t="inlineStr">
         <is>
-          <t>叶片终检放行</t>
+          <t>盘轴动平衡</t>
         </is>
       </c>
       <c r="D10" s="44" t="inlineStr"/>
       <c r="E10" s="44" t="inlineStr">
         <is>
-          <t>检验</t>
+          <t>加工</t>
         </is>
       </c>
       <c r="F10" s="44" t="inlineStr">
         <is>
-          <t>Wc303</t>
+          <t>WC-SH-01</t>
         </is>
       </c>
       <c r="G10" s="44" t="n">
         <v>8</v>
       </c>
       <c r="H10" s="44" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I10" s="44" t="inlineStr">
         <is>
@@ -4807,7 +4823,7 @@
       </c>
       <c r="L10" s="44" t="inlineStr">
         <is>
-          <t>完成叶片型面、流道和外观终检。</t>
+          <t>完成盘轴组件动平衡与修正。</t>
         </is>
       </c>
       <c r="M10" s="44" t="inlineStr">
@@ -4820,30 +4836,30 @@
       <c r="A11" s="44" t="inlineStr"/>
       <c r="B11" s="44" t="inlineStr">
         <is>
-          <t>装配专业</t>
+          <t>机械加工专业</t>
         </is>
       </c>
       <c r="C11" s="44" t="inlineStr">
         <is>
-          <t>齐套确认</t>
+          <t>盘轴终检</t>
         </is>
       </c>
       <c r="D11" s="44" t="inlineStr"/>
       <c r="E11" s="44" t="inlineStr">
         <is>
-          <t>加工</t>
+          <t>检验</t>
         </is>
       </c>
       <c r="F11" s="44" t="inlineStr">
         <is>
-          <t>Wc401</t>
+          <t>WC-QC-SH-01</t>
         </is>
       </c>
       <c r="G11" s="44" t="n">
         <v>8</v>
       </c>
       <c r="H11" s="44" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I11" s="44" t="inlineStr">
         <is>
@@ -4860,7 +4876,7 @@
       </c>
       <c r="L11" s="44" t="inlineStr">
         <is>
-          <t>完成机匣件、盘轴模块、叶片组件和装配配套件齐套确认。</t>
+          <t>完成盘轴组件终检与放行。</t>
         </is>
       </c>
       <c r="M11" s="44" t="inlineStr">
@@ -4873,12 +4889,12 @@
       <c r="A12" s="44" t="inlineStr"/>
       <c r="B12" s="44" t="inlineStr">
         <is>
-          <t>装配专业</t>
+          <t>机械加工专业</t>
         </is>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>整机总装</t>
+          <t>叶片成型</t>
         </is>
       </c>
       <c r="D12" s="44" t="inlineStr"/>
@@ -4889,14 +4905,14 @@
       </c>
       <c r="F12" s="44" t="inlineStr">
         <is>
-          <t>Wc401</t>
+          <t>WC-BL-01</t>
         </is>
       </c>
       <c r="G12" s="44" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H12" s="44" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I12" s="44" t="inlineStr">
         <is>
@@ -4913,7 +4929,7 @@
       </c>
       <c r="L12" s="44" t="inlineStr">
         <is>
-          <t>完成发动机核心机、盘轴和叶片相关总装联接。</t>
+          <t>完成叶片毛坯成型与修整。</t>
         </is>
       </c>
       <c r="M12" s="44" t="inlineStr">
@@ -4926,23 +4942,23 @@
       <c r="A13" s="44" t="inlineStr"/>
       <c r="B13" s="44" t="inlineStr">
         <is>
-          <t>装配专业</t>
+          <t>机械加工专业</t>
         </is>
       </c>
       <c r="C13" s="44" t="inlineStr">
         <is>
-          <t>整机试车与交付放行</t>
+          <t>叶片涂层</t>
         </is>
       </c>
       <c r="D13" s="44" t="inlineStr"/>
       <c r="E13" s="44" t="inlineStr">
         <is>
-          <t>检验</t>
+          <t>加工</t>
         </is>
       </c>
       <c r="F13" s="44" t="inlineStr">
         <is>
-          <t>Wc402</t>
+          <t>WC-BL-01</t>
         </is>
       </c>
       <c r="G13" s="44" t="n">
@@ -4966,7 +4982,7 @@
       </c>
       <c r="L13" s="44" t="inlineStr">
         <is>
-          <t>完成整机试车、质量结论和交付放行。</t>
+          <t>完成叶片保护涂层处理。</t>
         </is>
       </c>
       <c r="M13" s="44" t="inlineStr">
@@ -4984,25 +5000,25 @@
       </c>
       <c r="C14" s="44" t="inlineStr">
         <is>
-          <t>10-机加厂阶段完成</t>
+          <t>叶片终检</t>
         </is>
       </c>
       <c r="D14" s="44" t="inlineStr"/>
       <c r="E14" s="44" t="inlineStr">
         <is>
-          <t>加工</t>
+          <t>检验</t>
         </is>
       </c>
       <c r="F14" s="44" t="inlineStr">
         <is>
-          <t>Wc901</t>
+          <t>WC-QC-BL-01</t>
         </is>
       </c>
       <c r="G14" s="44" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="44" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I14" s="44" t="inlineStr">
         <is>
@@ -5019,7 +5035,7 @@
       </c>
       <c r="L14" s="44" t="inlineStr">
         <is>
-          <t>生产部确认机加厂机匣件完工与交付节拍。</t>
+          <t>完成叶片组件套终检与放行。</t>
         </is>
       </c>
       <c r="M14" s="44" t="inlineStr">
@@ -5032,12 +5048,12 @@
       <c r="A15" s="44" t="inlineStr"/>
       <c r="B15" s="44" t="inlineStr">
         <is>
-          <t>机械加工专业</t>
+          <t>装配专业</t>
         </is>
       </c>
       <c r="C15" s="44" t="inlineStr">
         <is>
-          <t>20-盘轴厂阶段完成</t>
+          <t>装配准备</t>
         </is>
       </c>
       <c r="D15" s="44" t="inlineStr"/>
@@ -5048,14 +5064,14 @@
       </c>
       <c r="F15" s="44" t="inlineStr">
         <is>
-          <t>Wc902</t>
+          <t>WC-ASM-01</t>
         </is>
       </c>
       <c r="G15" s="44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H15" s="44" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I15" s="44" t="inlineStr">
         <is>
@@ -5072,7 +5088,7 @@
       </c>
       <c r="L15" s="44" t="inlineStr">
         <is>
-          <t>生产部确认盘轴厂关键转子模块完工与交付节拍。</t>
+          <t>完成装配准备与齐套确认。</t>
         </is>
       </c>
       <c r="M15" s="44" t="inlineStr">
@@ -5085,12 +5101,12 @@
       <c r="A16" s="44" t="inlineStr"/>
       <c r="B16" s="44" t="inlineStr">
         <is>
-          <t>机械加工专业</t>
+          <t>装配专业</t>
         </is>
       </c>
       <c r="C16" s="44" t="inlineStr">
         <is>
-          <t>30-叶片厂阶段完成</t>
+          <t>总装</t>
         </is>
       </c>
       <c r="D16" s="44" t="inlineStr"/>
@@ -5101,14 +5117,14 @@
       </c>
       <c r="F16" s="44" t="inlineStr">
         <is>
-          <t>Wc903</t>
+          <t>WC-ASM-01</t>
         </is>
       </c>
       <c r="G16" s="44" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H16" s="44" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="I16" s="44" t="inlineStr">
         <is>
@@ -5125,7 +5141,7 @@
       </c>
       <c r="L16" s="44" t="inlineStr">
         <is>
-          <t>生产部确认叶片厂关键叶片组件完工与交付节拍。</t>
+          <t>完成发动机总装联接。</t>
         </is>
       </c>
       <c r="M16" s="44" t="inlineStr">
@@ -5143,7 +5159,7 @@
       </c>
       <c r="C17" s="44" t="inlineStr">
         <is>
-          <t>40-装配厂总装试车完成</t>
+          <t>完工装配</t>
         </is>
       </c>
       <c r="D17" s="44" t="inlineStr"/>
@@ -5154,14 +5170,14 @@
       </c>
       <c r="F17" s="44" t="inlineStr">
         <is>
-          <t>Wc904</t>
+          <t>WC-ASM-01</t>
         </is>
       </c>
       <c r="G17" s="44" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H17" s="44" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I17" s="44" t="inlineStr">
         <is>
@@ -5178,7 +5194,7 @@
       </c>
       <c r="L17" s="44" t="inlineStr">
         <is>
-          <t>生产部确认总装、试车和交付窗口，形成整机交付承诺。</t>
+          <t>完成完工装配、试车前状态确认与入库前准备。</t>
         </is>
       </c>
       <c r="M17" s="44" t="inlineStr">
@@ -8266,7 +8282,7 @@
       </c>
       <c r="B2" s="44" t="inlineStr">
         <is>
-          <t>GM-500</t>
+          <t>MC-500</t>
         </is>
       </c>
       <c r="C2" s="44" t="inlineStr">
@@ -8276,12 +8292,12 @@
       </c>
       <c r="D2" s="44" t="inlineStr">
         <is>
-          <t>Eq101</t>
+          <t>EQ-MC-01</t>
         </is>
       </c>
       <c r="E2" s="44" t="inlineStr">
         <is>
-          <t>机匣关键孔面加工</t>
+          <t>机匣组件关键孔面加工。</t>
         </is>
       </c>
       <c r="F2" s="44" t="inlineStr">
@@ -8296,12 +8312,12 @@
       </c>
       <c r="H2" s="44" t="inlineStr">
         <is>
-          <t>Eq101</t>
+          <t>EQ-MC-01</t>
         </is>
       </c>
       <c r="I2" s="44" t="inlineStr">
         <is>
-          <t>Biz012</t>
+          <t>ORG-MC-TM-001</t>
         </is>
       </c>
       <c r="J2" s="44" t="inlineStr"/>
@@ -8309,7 +8325,7 @@
     <row r="3">
       <c r="A3" s="44" t="inlineStr">
         <is>
-          <t>三坐标测量机</t>
+          <t>机匣三坐标测量机</t>
         </is>
       </c>
       <c r="B3" s="44" t="inlineStr">
@@ -8324,12 +8340,12 @@
       </c>
       <c r="D3" s="44" t="inlineStr">
         <is>
-          <t>Eq102</t>
+          <t>EQ-QC-MC-01</t>
         </is>
       </c>
       <c r="E3" s="44" t="inlineStr">
         <is>
-          <t>机匣尺寸测量</t>
+          <t>机匣组件尺寸终检。</t>
         </is>
       </c>
       <c r="F3" s="44" t="inlineStr">
@@ -8344,12 +8360,12 @@
       </c>
       <c r="H3" s="44" t="inlineStr">
         <is>
-          <t>Eq102</t>
+          <t>EQ-QC-MC-01</t>
         </is>
       </c>
       <c r="I3" s="44" t="inlineStr">
         <is>
-          <t>Biz013</t>
+          <t>ORG-MC-QC-001</t>
         </is>
       </c>
       <c r="J3" s="44" t="inlineStr"/>
@@ -8357,12 +8373,12 @@
     <row r="4">
       <c r="A4" s="44" t="inlineStr">
         <is>
-          <t>车铣复合机床</t>
+          <t>盘轴复合加工机</t>
         </is>
       </c>
       <c r="B4" s="44" t="inlineStr">
         <is>
-          <t>TM-600</t>
+          <t>SH-600</t>
         </is>
       </c>
       <c r="C4" s="44" t="inlineStr">
@@ -8372,12 +8388,12 @@
       </c>
       <c r="D4" s="44" t="inlineStr">
         <is>
-          <t>Eq201</t>
+          <t>EQ-SH-01</t>
         </is>
       </c>
       <c r="E4" s="44" t="inlineStr">
         <is>
-          <t>盘轴复合加工</t>
+          <t>盘轴组件复合加工与动平衡。</t>
         </is>
       </c>
       <c r="F4" s="44" t="inlineStr">
@@ -8392,12 +8408,12 @@
       </c>
       <c r="H4" s="44" t="inlineStr">
         <is>
-          <t>Eq201</t>
+          <t>EQ-SH-01</t>
         </is>
       </c>
       <c r="I4" s="44" t="inlineStr">
         <is>
-          <t>Biz022</t>
+          <t>ORG-SH-TM-001</t>
         </is>
       </c>
       <c r="J4" s="44" t="inlineStr"/>
@@ -8405,12 +8421,12 @@
     <row r="5">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>高速动平衡机</t>
+          <t>盘轴探伤检测台</t>
         </is>
       </c>
       <c r="B5" s="44" t="inlineStr">
         <is>
-          <t>DB-300</t>
+          <t>UT-200</t>
         </is>
       </c>
       <c r="C5" s="44" t="inlineStr">
@@ -8420,12 +8436,12 @@
       </c>
       <c r="D5" s="44" t="inlineStr">
         <is>
-          <t>Eq202</t>
+          <t>EQ-QC-SH-01</t>
         </is>
       </c>
       <c r="E5" s="44" t="inlineStr">
         <is>
-          <t>盘轴动平衡修正</t>
+          <t>盘轴组件超声终检。</t>
         </is>
       </c>
       <c r="F5" s="44" t="inlineStr">
@@ -8440,12 +8456,12 @@
       </c>
       <c r="H5" s="44" t="inlineStr">
         <is>
-          <t>Eq202</t>
+          <t>EQ-QC-SH-01</t>
         </is>
       </c>
       <c r="I5" s="44" t="inlineStr">
         <is>
-          <t>Biz023</t>
+          <t>ORG-SH-QC-001</t>
         </is>
       </c>
       <c r="J5" s="44" t="inlineStr"/>
@@ -8453,12 +8469,12 @@
     <row r="6">
       <c r="A6" s="44" t="inlineStr">
         <is>
-          <t>超声探伤台</t>
+          <t>叶片成型磨床</t>
         </is>
       </c>
       <c r="B6" s="44" t="inlineStr">
         <is>
-          <t>UT-80</t>
+          <t>BL-220</t>
         </is>
       </c>
       <c r="C6" s="44" t="inlineStr">
@@ -8468,12 +8484,12 @@
       </c>
       <c r="D6" s="44" t="inlineStr">
         <is>
-          <t>Eq203</t>
+          <t>EQ-BL-01</t>
         </is>
       </c>
       <c r="E6" s="44" t="inlineStr">
         <is>
-          <t>盘轴无损终检</t>
+          <t>叶片型面成型与修整。</t>
         </is>
       </c>
       <c r="F6" s="44" t="inlineStr">
@@ -8488,12 +8504,12 @@
       </c>
       <c r="H6" s="44" t="inlineStr">
         <is>
-          <t>Eq203</t>
+          <t>EQ-BL-01</t>
         </is>
       </c>
       <c r="I6" s="44" t="inlineStr">
         <is>
-          <t>Biz023</t>
+          <t>ORG-BL-TM-001</t>
         </is>
       </c>
       <c r="J6" s="44" t="inlineStr"/>
@@ -8501,12 +8517,12 @@
     <row r="7">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>叶片成型磨床</t>
+          <t>叶片流道检测台</t>
         </is>
       </c>
       <c r="B7" s="44" t="inlineStr">
         <is>
-          <t>LM-220</t>
+          <t>FL-30</t>
         </is>
       </c>
       <c r="C7" s="44" t="inlineStr">
@@ -8516,12 +8532,12 @@
       </c>
       <c r="D7" s="44" t="inlineStr">
         <is>
-          <t>Eq301</t>
+          <t>EQ-QC-BL-01</t>
         </is>
       </c>
       <c r="E7" s="44" t="inlineStr">
         <is>
-          <t>叶片型面成型</t>
+          <t>叶片流道与外观检测。</t>
         </is>
       </c>
       <c r="F7" s="44" t="inlineStr">
@@ -8536,12 +8552,12 @@
       </c>
       <c r="H7" s="44" t="inlineStr">
         <is>
-          <t>Eq301</t>
+          <t>EQ-QC-BL-01</t>
         </is>
       </c>
       <c r="I7" s="44" t="inlineStr">
         <is>
-          <t>Biz032</t>
+          <t>ORG-BL-QC-001</t>
         </is>
       </c>
       <c r="J7" s="44" t="inlineStr"/>
@@ -8549,12 +8565,12 @@
     <row r="8">
       <c r="A8" s="44" t="inlineStr">
         <is>
-          <t>涂层喷涂柜</t>
+          <t>发动机总装定位工位</t>
         </is>
       </c>
       <c r="B8" s="44" t="inlineStr">
         <is>
-          <t>TC-90</t>
+          <t>ASM-100</t>
         </is>
       </c>
       <c r="C8" s="44" t="inlineStr">
@@ -8564,12 +8580,12 @@
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>Eq302</t>
+          <t>EQ-ASM-01</t>
         </is>
       </c>
       <c r="E8" s="44" t="inlineStr">
         <is>
-          <t>叶片表面保护涂层</t>
+          <t>总装定位与联接。</t>
         </is>
       </c>
       <c r="F8" s="44" t="inlineStr">
@@ -8584,12 +8600,12 @@
       </c>
       <c r="H8" s="44" t="inlineStr">
         <is>
-          <t>Eq302</t>
+          <t>EQ-ASM-01</t>
         </is>
       </c>
       <c r="I8" s="44" t="inlineStr">
         <is>
-          <t>Biz032</t>
+          <t>ORG-AS-TM-001</t>
         </is>
       </c>
       <c r="J8" s="44" t="inlineStr"/>
@@ -8597,12 +8613,12 @@
     <row r="9">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>叶片流量检测台</t>
+          <t>发动机总装检验台</t>
         </is>
       </c>
       <c r="B9" s="44" t="inlineStr">
         <is>
-          <t>FL-30</t>
+          <t>QC-ASM-01</t>
         </is>
       </c>
       <c r="C9" s="44" t="inlineStr">
@@ -8612,12 +8628,12 @@
       </c>
       <c r="D9" s="44" t="inlineStr">
         <is>
-          <t>Eq303</t>
+          <t>EQ-QC-ASM-01</t>
         </is>
       </c>
       <c r="E9" s="44" t="inlineStr">
         <is>
-          <t>叶片流道与通流检测</t>
+          <t>首检、专检和总装终检。</t>
         </is>
       </c>
       <c r="F9" s="44" t="inlineStr">
@@ -8632,110 +8648,38 @@
       </c>
       <c r="H9" s="44" t="inlineStr">
         <is>
-          <t>Eq303</t>
+          <t>EQ-QC-ASM-01</t>
         </is>
       </c>
       <c r="I9" s="44" t="inlineStr">
         <is>
-          <t>Biz033</t>
+          <t>ORG-AS-QC-001</t>
         </is>
       </c>
       <c r="J9" s="44" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>总装定位工位</t>
-        </is>
-      </c>
-      <c r="B10" s="44" t="inlineStr">
-        <is>
-          <t>ASM-100</t>
-        </is>
-      </c>
-      <c r="C10" s="44" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D10" s="44" t="inlineStr">
-        <is>
-          <t>Eq401</t>
-        </is>
-      </c>
-      <c r="E10" s="44" t="inlineStr">
-        <is>
-          <t>整机总装定位与联接</t>
-        </is>
-      </c>
-      <c r="F10" s="44" t="inlineStr">
-        <is>
-          <t>公开</t>
-        </is>
-      </c>
-      <c r="G10" s="44" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="H10" s="44" t="inlineStr">
-        <is>
-          <t>Eq401</t>
-        </is>
-      </c>
-      <c r="I10" s="44" t="inlineStr">
-        <is>
-          <t>Biz042</t>
-        </is>
-      </c>
+      <c r="A10" s="44" t="inlineStr"/>
+      <c r="B10" s="44" t="inlineStr"/>
+      <c r="C10" s="44" t="inlineStr"/>
+      <c r="D10" s="44" t="inlineStr"/>
+      <c r="E10" s="44" t="inlineStr"/>
+      <c r="F10" s="44" t="inlineStr"/>
+      <c r="G10" s="44" t="inlineStr"/>
+      <c r="H10" s="44" t="inlineStr"/>
+      <c r="I10" s="44" t="inlineStr"/>
       <c r="J10" s="44" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>发动机试车台</t>
-        </is>
-      </c>
-      <c r="B11" s="44" t="inlineStr">
-        <is>
-          <t>TEST-900</t>
-        </is>
-      </c>
-      <c r="C11" s="44" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D11" s="44" t="inlineStr">
-        <is>
-          <t>Eq402</t>
-        </is>
-      </c>
-      <c r="E11" s="44" t="inlineStr">
-        <is>
-          <t>整机试车与放行</t>
-        </is>
-      </c>
-      <c r="F11" s="44" t="inlineStr">
-        <is>
-          <t>公开</t>
-        </is>
-      </c>
-      <c r="G11" s="44" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="H11" s="44" t="inlineStr">
-        <is>
-          <t>Eq402</t>
-        </is>
-      </c>
-      <c r="I11" s="44" t="inlineStr">
-        <is>
-          <t>Biz043</t>
-        </is>
-      </c>
+      <c r="A11" s="44" t="inlineStr"/>
+      <c r="B11" s="44" t="inlineStr"/>
+      <c r="C11" s="44" t="inlineStr"/>
+      <c r="D11" s="44" t="inlineStr"/>
+      <c r="E11" s="44" t="inlineStr"/>
+      <c r="F11" s="44" t="inlineStr"/>
+      <c r="G11" s="44" t="inlineStr"/>
+      <c r="H11" s="44" t="inlineStr"/>
+      <c r="I11" s="44" t="inlineStr"/>
       <c r="J11" s="44" t="inlineStr"/>
     </row>
     <row r="12">
@@ -9859,86 +9803,70 @@
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Eq101</t>
+          <t>EQ-MC-01</t>
         </is>
       </c>
       <c r="B2" s="44" t="inlineStr">
         <is>
-          <t>K2005</t>
+          <t>chengang</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="44" t="inlineStr">
         <is>
-          <t>Eq102</t>
+          <t>EQ-SH-01</t>
         </is>
       </c>
       <c r="B3" s="44" t="inlineStr">
         <is>
-          <t>K2006</t>
+          <t>hanbo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="44" t="inlineStr">
         <is>
-          <t>Eq201</t>
+          <t>EQ-BL-01</t>
         </is>
       </c>
       <c r="B4" s="44" t="inlineStr">
         <is>
-          <t>K2009</t>
+          <t>linna</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>Eq202</t>
+          <t>EQ-ASM-01</t>
         </is>
       </c>
       <c r="B5" s="44" t="inlineStr">
         <is>
-          <t>K2010</t>
+          <t>qianfeng</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="44" t="inlineStr">
         <is>
-          <t>Eq301</t>
+          <t>EQ-QC-ASM-01</t>
         </is>
       </c>
       <c r="B6" s="44" t="inlineStr">
         <is>
-          <t>K2013</t>
+          <t>sunjie</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="44" t="inlineStr">
-        <is>
-          <t>Eq401</t>
-        </is>
-      </c>
-      <c r="B7" s="44" t="inlineStr">
-        <is>
-          <t>K2017</t>
-        </is>
-      </c>
+      <c r="A7" s="44" t="inlineStr"/>
+      <c r="B7" s="44" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="44" t="inlineStr">
-        <is>
-          <t>Eq402</t>
-        </is>
-      </c>
-      <c r="B8" s="44" t="inlineStr">
-        <is>
-          <t>K2018</t>
-        </is>
-      </c>
+      <c r="A8" s="44" t="inlineStr"/>
+      <c r="B8" s="44" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="44" t="inlineStr"/>
@@ -10516,17 +10444,17 @@
       </c>
       <c r="D2" s="44" t="inlineStr">
         <is>
-          <t>Tool101</t>
+          <t>TOOL-MC-01</t>
         </is>
       </c>
       <c r="E2" s="44" t="inlineStr">
         <is>
-          <t>JJ-101</t>
+          <t>MC-JJ-01</t>
         </is>
       </c>
       <c r="F2" s="44" t="inlineStr">
         <is>
-          <t>机匣孔面定位</t>
+          <t>机匣找正定位</t>
         </is>
       </c>
       <c r="G2" s="44" t="inlineStr">
@@ -10564,7 +10492,7 @@
         </is>
       </c>
       <c r="Q2" s="44" t="n">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="R2" s="44" t="n">
         <v>365</v>
@@ -10591,12 +10519,12 @@
       </c>
       <c r="W2" s="44" t="inlineStr">
         <is>
-          <t>Tool101</t>
+          <t>TOOL-MC-01</t>
         </is>
       </c>
       <c r="X2" s="44" t="inlineStr">
         <is>
-          <t>机匣加工定位夹具</t>
+          <t>机加厂机匣组件专用定位夹具。</t>
         </is>
       </c>
       <c r="Y2" s="44" t="inlineStr">
@@ -10611,7 +10539,7 @@
       </c>
       <c r="AA2" s="44" t="inlineStr">
         <is>
-          <t>Tool101</t>
+          <t>TOOL-MC-01</t>
         </is>
       </c>
       <c r="AB2" s="44" t="inlineStr"/>
@@ -10624,7 +10552,7 @@
       </c>
       <c r="B3" s="44" t="inlineStr">
         <is>
-          <t>盘轴平衡工装</t>
+          <t>盘轴动平衡工装</t>
         </is>
       </c>
       <c r="C3" s="44" t="inlineStr">
@@ -10634,17 +10562,17 @@
       </c>
       <c r="D3" s="44" t="inlineStr">
         <is>
-          <t>Tool201</t>
+          <t>TOOL-SH-01</t>
         </is>
       </c>
       <c r="E3" s="44" t="inlineStr">
         <is>
-          <t>PJ-201</t>
+          <t>SH-PH-01</t>
         </is>
       </c>
       <c r="F3" s="44" t="inlineStr">
         <is>
-          <t>盘轴平衡修正</t>
+          <t>盘轴平衡校正</t>
         </is>
       </c>
       <c r="G3" s="44" t="inlineStr">
@@ -10682,7 +10610,7 @@
         </is>
       </c>
       <c r="Q3" s="44" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="R3" s="44" t="n">
         <v>365</v>
@@ -10709,12 +10637,12 @@
       </c>
       <c r="W3" s="44" t="inlineStr">
         <is>
-          <t>Tool201</t>
+          <t>TOOL-SH-01</t>
         </is>
       </c>
       <c r="X3" s="44" t="inlineStr">
         <is>
-          <t>盘轴平衡修正工装</t>
+          <t>盘轴厂动平衡修正工装。</t>
         </is>
       </c>
       <c r="Y3" s="44" t="inlineStr">
@@ -10729,7 +10657,7 @@
       </c>
       <c r="AA3" s="44" t="inlineStr">
         <is>
-          <t>Tool201</t>
+          <t>TOOL-SH-01</t>
         </is>
       </c>
       <c r="AB3" s="44" t="inlineStr"/>
@@ -10752,12 +10680,12 @@
       </c>
       <c r="D4" s="44" t="inlineStr">
         <is>
-          <t>Tool301</t>
+          <t>TOOL-BL-01</t>
         </is>
       </c>
       <c r="E4" s="44" t="inlineStr">
         <is>
-          <t>YJ-301</t>
+          <t>BL-JJ-01</t>
         </is>
       </c>
       <c r="F4" s="44" t="inlineStr">
@@ -10800,7 +10728,7 @@
         </is>
       </c>
       <c r="Q4" s="44" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="R4" s="44" t="n">
         <v>365</v>
@@ -10827,12 +10755,12 @@
       </c>
       <c r="W4" s="44" t="inlineStr">
         <is>
-          <t>Tool301</t>
+          <t>TOOL-BL-01</t>
         </is>
       </c>
       <c r="X4" s="44" t="inlineStr">
         <is>
-          <t>叶片型面快速检测检具</t>
+          <t>叶片厂型面快速检测检具。</t>
         </is>
       </c>
       <c r="Y4" s="44" t="inlineStr">
@@ -10847,7 +10775,7 @@
       </c>
       <c r="AA4" s="44" t="inlineStr">
         <is>
-          <t>Tool301</t>
+          <t>TOOL-BL-01</t>
         </is>
       </c>
       <c r="AB4" s="44" t="inlineStr"/>
@@ -10860,7 +10788,7 @@
       </c>
       <c r="B5" s="44" t="inlineStr">
         <is>
-          <t>整机总装吊具</t>
+          <t>发动机总装吊具</t>
         </is>
       </c>
       <c r="C5" s="44" t="inlineStr">
@@ -10870,12 +10798,12 @@
       </c>
       <c r="D5" s="44" t="inlineStr">
         <is>
-          <t>Tool401</t>
+          <t>TOOL-ASM-01</t>
         </is>
       </c>
       <c r="E5" s="44" t="inlineStr">
         <is>
-          <t>DJ-401</t>
+          <t>ASM-DJ-01</t>
         </is>
       </c>
       <c r="F5" s="44" t="inlineStr">
@@ -10945,12 +10873,12 @@
       </c>
       <c r="W5" s="44" t="inlineStr">
         <is>
-          <t>Tool401</t>
+          <t>TOOL-ASM-01</t>
         </is>
       </c>
       <c r="X5" s="44" t="inlineStr">
         <is>
-          <t>整机总装吊具</t>
+          <t>装配厂总装吊装定位工装。</t>
         </is>
       </c>
       <c r="Y5" s="44" t="inlineStr">
@@ -10965,7 +10893,7 @@
       </c>
       <c r="AA5" s="44" t="inlineStr">
         <is>
-          <t>Tool401</t>
+          <t>TOOL-ASM-01</t>
         </is>
       </c>
       <c r="AB5" s="44" t="inlineStr"/>
@@ -15462,7 +15390,7 @@
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>机匣机加中心</t>
+          <t>10-机加厂协同中心</t>
         </is>
       </c>
       <c r="B2" s="44" t="inlineStr">
@@ -15477,12 +15405,12 @@
       </c>
       <c r="D2" s="44" t="inlineStr">
         <is>
-          <t>Wc101</t>
+          <t>WC-PD-MC-01</t>
         </is>
       </c>
       <c r="E2" s="44" t="inlineStr">
         <is>
-          <t>负责机匣找正、粗精加工</t>
+          <t>一级工艺阶段 10-机加厂。</t>
         </is>
       </c>
       <c r="F2" s="44" t="inlineStr">
@@ -15497,12 +15425,12 @@
       </c>
       <c r="H2" s="44" t="inlineStr">
         <is>
-          <t>Wc101</t>
+          <t>WC-PD-MC-01</t>
         </is>
       </c>
       <c r="I2" s="44" t="inlineStr">
         <is>
-          <t>Biz012</t>
+          <t>ORG-PD-001</t>
         </is>
       </c>
       <c r="J2" s="44" t="inlineStr"/>
@@ -15510,7 +15438,7 @@
     <row r="3">
       <c r="A3" s="44" t="inlineStr">
         <is>
-          <t>机匣尺寸检验中心</t>
+          <t>20-盘轴厂协同中心</t>
         </is>
       </c>
       <c r="B3" s="44" t="inlineStr">
@@ -15520,17 +15448,17 @@
       </c>
       <c r="C3" s="44" t="inlineStr">
         <is>
-          <t>检验</t>
+          <t>加工</t>
         </is>
       </c>
       <c r="D3" s="44" t="inlineStr">
         <is>
-          <t>Wc102</t>
+          <t>WC-PD-SH-01</t>
         </is>
       </c>
       <c r="E3" s="44" t="inlineStr">
         <is>
-          <t>负责机加尺寸、同轴度和表面质量放行</t>
+          <t>一级工艺阶段 20-盘轴厂。</t>
         </is>
       </c>
       <c r="F3" s="44" t="inlineStr">
@@ -15545,12 +15473,12 @@
       </c>
       <c r="H3" s="44" t="inlineStr">
         <is>
-          <t>Wc102</t>
+          <t>WC-PD-SH-01</t>
         </is>
       </c>
       <c r="I3" s="44" t="inlineStr">
         <is>
-          <t>Biz013</t>
+          <t>ORG-PD-001</t>
         </is>
       </c>
       <c r="J3" s="44" t="inlineStr"/>
@@ -15558,7 +15486,7 @@
     <row r="4">
       <c r="A4" s="44" t="inlineStr">
         <is>
-          <t>盘轴复合加工中心</t>
+          <t>30-叶片厂协同中心</t>
         </is>
       </c>
       <c r="B4" s="44" t="inlineStr">
@@ -15573,12 +15501,12 @@
       </c>
       <c r="D4" s="44" t="inlineStr">
         <is>
-          <t>Wc201</t>
+          <t>WC-PD-BL-01</t>
         </is>
       </c>
       <c r="E4" s="44" t="inlineStr">
         <is>
-          <t>负责盘轴类关键件车铣复合加工</t>
+          <t>一级工艺阶段 30-叶片厂。</t>
         </is>
       </c>
       <c r="F4" s="44" t="inlineStr">
@@ -15593,12 +15521,12 @@
       </c>
       <c r="H4" s="44" t="inlineStr">
         <is>
-          <t>Wc201</t>
+          <t>WC-PD-BL-01</t>
         </is>
       </c>
       <c r="I4" s="44" t="inlineStr">
         <is>
-          <t>Biz022</t>
+          <t>ORG-PD-001</t>
         </is>
       </c>
       <c r="J4" s="44" t="inlineStr"/>
@@ -15606,7 +15534,7 @@
     <row r="5">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>盘轴动平衡中心</t>
+          <t>40-装配厂协同中心</t>
         </is>
       </c>
       <c r="B5" s="44" t="inlineStr">
@@ -15621,12 +15549,12 @@
       </c>
       <c r="D5" s="44" t="inlineStr">
         <is>
-          <t>Wc202</t>
+          <t>WC-PD-AS-01</t>
         </is>
       </c>
       <c r="E5" s="44" t="inlineStr">
         <is>
-          <t>负责盘轴动平衡修正与配重</t>
+          <t>一级工艺阶段 40-装配厂。</t>
         </is>
       </c>
       <c r="F5" s="44" t="inlineStr">
@@ -15641,12 +15569,12 @@
       </c>
       <c r="H5" s="44" t="inlineStr">
         <is>
-          <t>Wc202</t>
+          <t>WC-PD-AS-01</t>
         </is>
       </c>
       <c r="I5" s="44" t="inlineStr">
         <is>
-          <t>Biz023</t>
+          <t>ORG-PD-001</t>
         </is>
       </c>
       <c r="J5" s="44" t="inlineStr"/>
@@ -15654,7 +15582,7 @@
     <row r="6">
       <c r="A6" s="44" t="inlineStr">
         <is>
-          <t>盘轴终检中心</t>
+          <t>机加粗加工中心</t>
         </is>
       </c>
       <c r="B6" s="44" t="inlineStr">
@@ -15664,17 +15592,17 @@
       </c>
       <c r="C6" s="44" t="inlineStr">
         <is>
-          <t>检验</t>
+          <t>加工</t>
         </is>
       </c>
       <c r="D6" s="44" t="inlineStr">
         <is>
-          <t>Wc203</t>
+          <t>WC-MC-01</t>
         </is>
       </c>
       <c r="E6" s="44" t="inlineStr">
         <is>
-          <t>负责盘轴探伤与尺寸终检</t>
+          <t>机匣组件粗精加工。</t>
         </is>
       </c>
       <c r="F6" s="44" t="inlineStr">
@@ -15689,12 +15617,12 @@
       </c>
       <c r="H6" s="44" t="inlineStr">
         <is>
-          <t>Wc203</t>
+          <t>WC-MC-01</t>
         </is>
       </c>
       <c r="I6" s="44" t="inlineStr">
         <is>
-          <t>Biz023</t>
+          <t>ORG-MC-TM-001</t>
         </is>
       </c>
       <c r="J6" s="44" t="inlineStr"/>
@@ -15702,7 +15630,7 @@
     <row r="7">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>叶片成型中心</t>
+          <t>机加尺寸检验中心</t>
         </is>
       </c>
       <c r="B7" s="44" t="inlineStr">
@@ -15712,17 +15640,17 @@
       </c>
       <c r="C7" s="44" t="inlineStr">
         <is>
-          <t>加工</t>
+          <t>检验</t>
         </is>
       </c>
       <c r="D7" s="44" t="inlineStr">
         <is>
-          <t>Wc301</t>
+          <t>WC-QC-MC-01</t>
         </is>
       </c>
       <c r="E7" s="44" t="inlineStr">
         <is>
-          <t>负责叶片型面成型与冷端修整</t>
+          <t>机匣组件终检放行。</t>
         </is>
       </c>
       <c r="F7" s="44" t="inlineStr">
@@ -15737,12 +15665,12 @@
       </c>
       <c r="H7" s="44" t="inlineStr">
         <is>
-          <t>Wc301</t>
+          <t>WC-QC-MC-01</t>
         </is>
       </c>
       <c r="I7" s="44" t="inlineStr">
         <is>
-          <t>Biz032</t>
+          <t>ORG-MC-QC-001</t>
         </is>
       </c>
       <c r="J7" s="44" t="inlineStr"/>
@@ -15750,7 +15678,7 @@
     <row r="8">
       <c r="A8" s="44" t="inlineStr">
         <is>
-          <t>叶片涂层中心</t>
+          <t>盘轴加工中心</t>
         </is>
       </c>
       <c r="B8" s="44" t="inlineStr">
@@ -15765,12 +15693,12 @@
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>Wc302</t>
+          <t>WC-SH-01</t>
         </is>
       </c>
       <c r="E8" s="44" t="inlineStr">
         <is>
-          <t>负责叶片保护涂层与固化</t>
+          <t>盘轴组件加工与平衡。</t>
         </is>
       </c>
       <c r="F8" s="44" t="inlineStr">
@@ -15785,12 +15713,12 @@
       </c>
       <c r="H8" s="44" t="inlineStr">
         <is>
-          <t>Wc302</t>
+          <t>WC-SH-01</t>
         </is>
       </c>
       <c r="I8" s="44" t="inlineStr">
         <is>
-          <t>Biz032</t>
+          <t>ORG-SH-TM-001</t>
         </is>
       </c>
       <c r="J8" s="44" t="inlineStr"/>
@@ -15798,7 +15726,7 @@
     <row r="9">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>叶片检测中心</t>
+          <t>盘轴终检中心</t>
         </is>
       </c>
       <c r="B9" s="44" t="inlineStr">
@@ -15813,12 +15741,12 @@
       </c>
       <c r="D9" s="44" t="inlineStr">
         <is>
-          <t>Wc303</t>
+          <t>WC-QC-SH-01</t>
         </is>
       </c>
       <c r="E9" s="44" t="inlineStr">
         <is>
-          <t>负责叶片流道、型面和外观终检</t>
+          <t>盘轴组件终检放行。</t>
         </is>
       </c>
       <c r="F9" s="44" t="inlineStr">
@@ -15833,12 +15761,12 @@
       </c>
       <c r="H9" s="44" t="inlineStr">
         <is>
-          <t>Wc303</t>
+          <t>WC-QC-SH-01</t>
         </is>
       </c>
       <c r="I9" s="44" t="inlineStr">
         <is>
-          <t>Biz033</t>
+          <t>ORG-SH-QC-001</t>
         </is>
       </c>
       <c r="J9" s="44" t="inlineStr"/>
@@ -15846,7 +15774,7 @@
     <row r="10">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>整机总装中心</t>
+          <t>叶片加工中心</t>
         </is>
       </c>
       <c r="B10" s="44" t="inlineStr">
@@ -15861,12 +15789,12 @@
       </c>
       <c r="D10" s="44" t="inlineStr">
         <is>
-          <t>Wc401</t>
+          <t>WC-BL-01</t>
         </is>
       </c>
       <c r="E10" s="44" t="inlineStr">
         <is>
-          <t>负责整机总装、联接和复核</t>
+          <t>叶片组件成型与涂层。</t>
         </is>
       </c>
       <c r="F10" s="44" t="inlineStr">
@@ -15881,12 +15809,12 @@
       </c>
       <c r="H10" s="44" t="inlineStr">
         <is>
-          <t>Wc401</t>
+          <t>WC-BL-01</t>
         </is>
       </c>
       <c r="I10" s="44" t="inlineStr">
         <is>
-          <t>Biz042</t>
+          <t>ORG-BL-TM-001</t>
         </is>
       </c>
       <c r="J10" s="44" t="inlineStr"/>
@@ -15894,7 +15822,7 @@
     <row r="11">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>整机试车放行中心</t>
+          <t>叶片终检中心</t>
         </is>
       </c>
       <c r="B11" s="44" t="inlineStr">
@@ -15909,12 +15837,12 @@
       </c>
       <c r="D11" s="44" t="inlineStr">
         <is>
-          <t>Wc402</t>
+          <t>WC-QC-BL-01</t>
         </is>
       </c>
       <c r="E11" s="44" t="inlineStr">
         <is>
-          <t>负责试车、质量结论和交付放行</t>
+          <t>叶片组件终检放行。</t>
         </is>
       </c>
       <c r="F11" s="44" t="inlineStr">
@@ -15929,12 +15857,12 @@
       </c>
       <c r="H11" s="44" t="inlineStr">
         <is>
-          <t>Wc402</t>
+          <t>WC-QC-BL-01</t>
         </is>
       </c>
       <c r="I11" s="44" t="inlineStr">
         <is>
-          <t>Biz043</t>
+          <t>ORG-BL-QC-001</t>
         </is>
       </c>
       <c r="J11" s="44" t="inlineStr"/>
@@ -15942,7 +15870,7 @@
     <row r="12">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>10-机加厂协同中心</t>
+          <t>总装工作中心</t>
         </is>
       </c>
       <c r="B12" s="44" t="inlineStr">
@@ -15957,12 +15885,12 @@
       </c>
       <c r="D12" s="44" t="inlineStr">
         <is>
-          <t>Wc901</t>
+          <t>WC-ASM-01</t>
         </is>
       </c>
       <c r="E12" s="44" t="inlineStr">
         <is>
-          <t>10-机加厂阶段完成对应的项目部协同排产中心</t>
+          <t>总装准备、总装与完工装配。</t>
         </is>
       </c>
       <c r="F12" s="44" t="inlineStr">
@@ -15977,12 +15905,12 @@
       </c>
       <c r="H12" s="44" t="inlineStr">
         <is>
-          <t>Wc901</t>
+          <t>WC-ASM-01</t>
         </is>
       </c>
       <c r="I12" s="44" t="inlineStr">
         <is>
-          <t>Biz900</t>
+          <t>ORG-AS-TM-001</t>
         </is>
       </c>
       <c r="J12" s="44" t="inlineStr"/>
@@ -15990,7 +15918,7 @@
     <row r="13">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>20-盘轴厂协同中心</t>
+          <t>总装检验中心</t>
         </is>
       </c>
       <c r="B13" s="44" t="inlineStr">
@@ -16000,17 +15928,17 @@
       </c>
       <c r="C13" s="44" t="inlineStr">
         <is>
-          <t>加工</t>
+          <t>检验</t>
         </is>
       </c>
       <c r="D13" s="44" t="inlineStr">
         <is>
-          <t>Wc902</t>
+          <t>WC-QC-ASM-01</t>
         </is>
       </c>
       <c r="E13" s="44" t="inlineStr">
         <is>
-          <t>20-盘轴厂阶段完成对应的项目部协同排产中心</t>
+          <t>装配厂首检、专检与放行检验。</t>
         </is>
       </c>
       <c r="F13" s="44" t="inlineStr">
@@ -16025,110 +15953,38 @@
       </c>
       <c r="H13" s="44" t="inlineStr">
         <is>
-          <t>Wc902</t>
+          <t>WC-QC-ASM-01</t>
         </is>
       </c>
       <c r="I13" s="44" t="inlineStr">
         <is>
-          <t>Biz900</t>
+          <t>ORG-AS-QC-001</t>
         </is>
       </c>
       <c r="J13" s="44" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="44" t="inlineStr">
-        <is>
-          <t>30-叶片厂协同中心</t>
-        </is>
-      </c>
-      <c r="B14" s="44" t="inlineStr">
-        <is>
-          <t>组织</t>
-        </is>
-      </c>
-      <c r="C14" s="44" t="inlineStr">
-        <is>
-          <t>加工</t>
-        </is>
-      </c>
-      <c r="D14" s="44" t="inlineStr">
-        <is>
-          <t>Wc903</t>
-        </is>
-      </c>
-      <c r="E14" s="44" t="inlineStr">
-        <is>
-          <t>30-叶片厂阶段完成对应的项目部协同排产中心</t>
-        </is>
-      </c>
-      <c r="F14" s="44" t="inlineStr">
-        <is>
-          <t>公开</t>
-        </is>
-      </c>
-      <c r="G14" s="44" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="H14" s="44" t="inlineStr">
-        <is>
-          <t>Wc903</t>
-        </is>
-      </c>
-      <c r="I14" s="44" t="inlineStr">
-        <is>
-          <t>Biz900</t>
-        </is>
-      </c>
+      <c r="A14" s="44" t="inlineStr"/>
+      <c r="B14" s="44" t="inlineStr"/>
+      <c r="C14" s="44" t="inlineStr"/>
+      <c r="D14" s="44" t="inlineStr"/>
+      <c r="E14" s="44" t="inlineStr"/>
+      <c r="F14" s="44" t="inlineStr"/>
+      <c r="G14" s="44" t="inlineStr"/>
+      <c r="H14" s="44" t="inlineStr"/>
+      <c r="I14" s="44" t="inlineStr"/>
       <c r="J14" s="44" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>40-装配厂协同中心</t>
-        </is>
-      </c>
-      <c r="B15" s="44" t="inlineStr">
-        <is>
-          <t>组织</t>
-        </is>
-      </c>
-      <c r="C15" s="44" t="inlineStr">
-        <is>
-          <t>加工</t>
-        </is>
-      </c>
-      <c r="D15" s="44" t="inlineStr">
-        <is>
-          <t>Wc904</t>
-        </is>
-      </c>
-      <c r="E15" s="44" t="inlineStr">
-        <is>
-          <t>40-装配厂总装试车完成对应的项目部协同排产中心</t>
-        </is>
-      </c>
-      <c r="F15" s="44" t="inlineStr">
-        <is>
-          <t>公开</t>
-        </is>
-      </c>
-      <c r="G15" s="44" t="inlineStr">
-        <is>
-          <t>MOM-SEED</t>
-        </is>
-      </c>
-      <c r="H15" s="44" t="inlineStr">
-        <is>
-          <t>Wc904</t>
-        </is>
-      </c>
-      <c r="I15" s="44" t="inlineStr">
-        <is>
-          <t>Biz900</t>
-        </is>
-      </c>
+      <c r="A15" s="44" t="inlineStr"/>
+      <c r="B15" s="44" t="inlineStr"/>
+      <c r="C15" s="44" t="inlineStr"/>
+      <c r="D15" s="44" t="inlineStr"/>
+      <c r="E15" s="44" t="inlineStr"/>
+      <c r="F15" s="44" t="inlineStr"/>
+      <c r="G15" s="44" t="inlineStr"/>
+      <c r="H15" s="44" t="inlineStr"/>
+      <c r="I15" s="44" t="inlineStr"/>
       <c r="J15" s="44" t="inlineStr"/>
     </row>
     <row r="16">
@@ -17207,120 +17063,120 @@
     <row r="2">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Wc101</t>
+          <t>WC-PD-MC-01</t>
         </is>
       </c>
       <c r="B2" s="44" t="inlineStr">
         <is>
-          <t>K2004</t>
+          <t>liumin</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="44" t="inlineStr">
         <is>
-          <t>Wc102</t>
+          <t>WC-PD-SH-01</t>
         </is>
       </c>
       <c r="B3" s="44" t="inlineStr">
         <is>
-          <t>K2006</t>
+          <t>liumin</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="44" t="inlineStr">
         <is>
-          <t>Wc201</t>
+          <t>WC-PD-BL-01</t>
         </is>
       </c>
       <c r="B4" s="44" t="inlineStr">
         <is>
-          <t>K2008</t>
+          <t>liumin</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>Wc202</t>
+          <t>WC-PD-AS-01</t>
         </is>
       </c>
       <c r="B5" s="44" t="inlineStr">
         <is>
-          <t>K2009</t>
+          <t>liumin</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="44" t="inlineStr">
         <is>
-          <t>Wc203</t>
+          <t>WC-MC-01</t>
         </is>
       </c>
       <c r="B6" s="44" t="inlineStr">
         <is>
-          <t>K2010</t>
+          <t>chengang</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>Wc301</t>
+          <t>WC-SH-01</t>
         </is>
       </c>
       <c r="B7" s="44" t="inlineStr">
         <is>
-          <t>K2012</t>
+          <t>hanbo</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="44" t="inlineStr">
         <is>
-          <t>Wc302</t>
+          <t>WC-BL-01</t>
         </is>
       </c>
       <c r="B8" s="44" t="inlineStr">
         <is>
-          <t>K2013</t>
+          <t>linna</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>Wc303</t>
+          <t>WC-ASM-01</t>
         </is>
       </c>
       <c r="B9" s="44" t="inlineStr">
         <is>
-          <t>K2014</t>
+          <t>zhaoyun</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>Wc401</t>
+          <t>WC-ASM-01</t>
         </is>
       </c>
       <c r="B10" s="44" t="inlineStr">
         <is>
-          <t>K2016</t>
+          <t>qianfeng</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>Wc402</t>
+          <t>WC-QC-ASM-01</t>
         </is>
       </c>
       <c r="B11" s="44" t="inlineStr">
         <is>
-          <t>K2018</t>
+          <t>sunjie</t>
         </is>
       </c>
     </row>
